--- a/research/traditional_assets/database/data/botswana/botswana_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/botswana/botswana_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0354</v>
+        <v>0.151</v>
       </c>
       <c r="E2">
-        <v>-0.0353</v>
+        <v>-0.00471</v>
       </c>
       <c r="G2">
-        <v>0.1359633673828813</v>
+        <v>0.05479930191972077</v>
       </c>
       <c r="H2">
-        <v>0.1359633673828813</v>
+        <v>0.05479930191972077</v>
       </c>
       <c r="I2">
-        <v>0.103557590700951</v>
+        <v>0.07713787085514835</v>
       </c>
       <c r="J2">
-        <v>0.0832671940016889</v>
+        <v>0.06149324206915831</v>
       </c>
       <c r="K2">
-        <v>42.9</v>
+        <v>36.5</v>
       </c>
       <c r="L2">
-        <v>0.1511095456146531</v>
+        <v>0.1273996509598604</v>
       </c>
       <c r="M2">
-        <v>36</v>
+        <v>17.4</v>
       </c>
       <c r="N2">
-        <v>0.08520710059171598</v>
+        <v>0.04471858134155744</v>
       </c>
       <c r="O2">
-        <v>0.8391608391608392</v>
+        <v>0.4767123287671233</v>
       </c>
       <c r="P2">
-        <v>36</v>
+        <v>17.4</v>
       </c>
       <c r="Q2">
-        <v>0.08520710059171598</v>
+        <v>0.04471858134155744</v>
       </c>
       <c r="R2">
-        <v>0.8391608391608392</v>
+        <v>0.4767123287671233</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>18.6</v>
+        <v>11.4</v>
       </c>
       <c r="V2">
-        <v>0.04402366863905326</v>
+        <v>0.02929838087895142</v>
       </c>
       <c r="W2">
-        <v>0.1720818291215403</v>
+        <v>0.1303571428571429</v>
       </c>
       <c r="X2">
-        <v>0.05242693255085718</v>
+        <v>0.08774507814732951</v>
       </c>
       <c r="Y2">
-        <v>0.1196548965706831</v>
+        <v>0.04261206470981335</v>
       </c>
       <c r="Z2">
-        <v>1.176738788029512</v>
+        <v>1.090514616321559</v>
       </c>
       <c r="AA2">
-        <v>0.09798373695216563</v>
+        <v>0.06705927928141693</v>
       </c>
       <c r="AB2">
-        <v>0.05236378422711802</v>
+        <v>0.08767459892307401</v>
       </c>
       <c r="AC2">
-        <v>0.0456199527250476</v>
+        <v>-0.02061531964165708</v>
       </c>
       <c r="AD2">
-        <v>1.32</v>
+        <v>0.903</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.32</v>
+        <v>0.903</v>
       </c>
       <c r="AG2">
-        <v>-17.28</v>
+        <v>-10.497</v>
       </c>
       <c r="AH2">
-        <v>0.003114529753197112</v>
+        <v>0.002315366804870731</v>
       </c>
       <c r="AI2">
-        <v>0.004652474270407445</v>
+        <v>0.003280022375346437</v>
       </c>
       <c r="AJ2">
-        <v>-0.0426435022950496</v>
+        <v>-0.02772561231685961</v>
       </c>
       <c r="AK2">
-        <v>-0.06517803258901629</v>
+        <v>-0.03977597829505539</v>
       </c>
       <c r="AL2">
-        <v>0.067</v>
+        <v>0.045</v>
       </c>
       <c r="AM2">
-        <v>0.067</v>
+        <v>0.045</v>
       </c>
       <c r="AN2">
-        <v>0.044</v>
+        <v>0.03875536480686696</v>
       </c>
       <c r="AO2">
-        <v>438.8059701492537</v>
+        <v>491.1111111111111</v>
       </c>
       <c r="AP2">
-        <v>-0.5760000000000001</v>
+        <v>-0.4505150214592274</v>
       </c>
       <c r="AQ2">
-        <v>438.8059701492537</v>
+        <v>491.1111111111111</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0354</v>
+        <v>0.151</v>
       </c>
       <c r="E3">
-        <v>-0.0353</v>
+        <v>-0.00471</v>
       </c>
       <c r="G3">
-        <v>0.1359633673828813</v>
+        <v>0.05479930191972077</v>
       </c>
       <c r="H3">
-        <v>0.1359633673828813</v>
+        <v>0.05479930191972077</v>
       </c>
       <c r="I3">
-        <v>0.103557590700951</v>
+        <v>0.07713787085514835</v>
       </c>
       <c r="J3">
-        <v>0.0832671940016889</v>
+        <v>0.06149324206915831</v>
       </c>
       <c r="K3">
-        <v>42.9</v>
+        <v>36.5</v>
       </c>
       <c r="L3">
-        <v>0.1511095456146531</v>
+        <v>0.1273996509598604</v>
       </c>
       <c r="M3">
-        <v>36</v>
+        <v>17.4</v>
       </c>
       <c r="N3">
-        <v>0.08520710059171598</v>
+        <v>0.04471858134155744</v>
       </c>
       <c r="O3">
-        <v>0.8391608391608392</v>
+        <v>0.4767123287671233</v>
       </c>
       <c r="P3">
-        <v>36</v>
+        <v>17.4</v>
       </c>
       <c r="Q3">
-        <v>0.08520710059171598</v>
+        <v>0.04471858134155744</v>
       </c>
       <c r="R3">
-        <v>0.8391608391608392</v>
+        <v>0.4767123287671233</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>18.6</v>
+        <v>11.4</v>
       </c>
       <c r="V3">
-        <v>0.04402366863905326</v>
+        <v>0.02929838087895142</v>
       </c>
       <c r="W3">
-        <v>0.1720818291215403</v>
+        <v>0.1303571428571429</v>
       </c>
       <c r="X3">
-        <v>0.05242693255085718</v>
+        <v>0.08774507814732951</v>
       </c>
       <c r="Y3">
-        <v>0.1196548965706831</v>
+        <v>0.04261206470981335</v>
       </c>
       <c r="Z3">
-        <v>1.176738788029512</v>
+        <v>1.090514616321559</v>
       </c>
       <c r="AA3">
-        <v>0.09798373695216563</v>
+        <v>0.06705927928141693</v>
       </c>
       <c r="AB3">
-        <v>0.05236378422711802</v>
+        <v>0.08767459892307401</v>
       </c>
       <c r="AC3">
-        <v>0.0456199527250476</v>
+        <v>-0.02061531964165708</v>
       </c>
       <c r="AD3">
-        <v>1.32</v>
+        <v>0.903</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.32</v>
+        <v>0.903</v>
       </c>
       <c r="AG3">
-        <v>-17.28</v>
+        <v>-10.497</v>
       </c>
       <c r="AH3">
-        <v>0.003114529753197112</v>
+        <v>0.002315366804870731</v>
       </c>
       <c r="AI3">
-        <v>0.004652474270407445</v>
+        <v>0.003280022375346437</v>
       </c>
       <c r="AJ3">
-        <v>-0.0426435022950496</v>
+        <v>-0.02772561231685961</v>
       </c>
       <c r="AK3">
-        <v>-0.06517803258901629</v>
+        <v>-0.03977597829505539</v>
       </c>
       <c r="AL3">
-        <v>0.067</v>
+        <v>0.045</v>
       </c>
       <c r="AM3">
-        <v>0.067</v>
+        <v>0.045</v>
       </c>
       <c r="AN3">
-        <v>0.044</v>
+        <v>0.03875536480686696</v>
       </c>
       <c r="AO3">
-        <v>438.8059701492537</v>
+        <v>491.1111111111111</v>
       </c>
       <c r="AP3">
-        <v>-0.5760000000000001</v>
+        <v>-0.4505150214592274</v>
       </c>
       <c r="AQ3">
-        <v>438.8059701492537</v>
+        <v>491.1111111111111</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/botswana/botswana_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/botswana/botswana_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.151</v>
+        <v>0.0496</v>
       </c>
       <c r="E2">
-        <v>-0.00471</v>
+        <v>0.181</v>
       </c>
       <c r="G2">
-        <v>0.05479930191972077</v>
+        <v>0.1344137273593899</v>
       </c>
       <c r="H2">
-        <v>0.05479930191972077</v>
+        <v>0.1344137273593899</v>
       </c>
       <c r="I2">
-        <v>0.07713787085514835</v>
+        <v>0.1944709246901812</v>
       </c>
       <c r="J2">
-        <v>0.06149324206915831</v>
+        <v>0.1558699120004216</v>
       </c>
       <c r="K2">
-        <v>36.5</v>
+        <v>63.2</v>
       </c>
       <c r="L2">
-        <v>0.1273996509598604</v>
+        <v>0.2008261836669845</v>
       </c>
       <c r="M2">
-        <v>17.4</v>
+        <v>55.2</v>
       </c>
       <c r="N2">
-        <v>0.04471858134155744</v>
+        <v>0.1299740993642571</v>
       </c>
       <c r="O2">
-        <v>0.4767123287671233</v>
+        <v>0.8734177215189873</v>
       </c>
       <c r="P2">
-        <v>17.4</v>
+        <v>55.2</v>
       </c>
       <c r="Q2">
-        <v>0.04471858134155744</v>
+        <v>0.1299740993642571</v>
       </c>
       <c r="R2">
-        <v>0.4767123287671233</v>
+        <v>0.8734177215189873</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>11.4</v>
+        <v>20.8</v>
       </c>
       <c r="V2">
-        <v>0.02929838087895142</v>
+        <v>0.04897574758653167</v>
       </c>
       <c r="W2">
-        <v>0.1303571428571429</v>
+        <v>0.2315018315018315</v>
       </c>
       <c r="X2">
-        <v>0.08774507814732951</v>
+        <v>0.0784179044057553</v>
       </c>
       <c r="Y2">
-        <v>0.04261206470981335</v>
+        <v>0.1530839270960762</v>
       </c>
       <c r="Z2">
-        <v>1.090514616321559</v>
+        <v>1.198843441789236</v>
       </c>
       <c r="AA2">
-        <v>0.06705927928141693</v>
+        <v>0.1868636217739708</v>
       </c>
       <c r="AB2">
-        <v>0.08767459892307401</v>
+        <v>0.07834271670054013</v>
       </c>
       <c r="AC2">
-        <v>-0.02061531964165708</v>
+        <v>0.1085209050734307</v>
       </c>
       <c r="AD2">
-        <v>0.903</v>
+        <v>0.967</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.903</v>
+        <v>0.967</v>
       </c>
       <c r="AG2">
-        <v>-10.497</v>
+        <v>-19.833</v>
       </c>
       <c r="AH2">
-        <v>0.002315366804870731</v>
+        <v>0.002271728839679844</v>
       </c>
       <c r="AI2">
-        <v>0.003280022375346437</v>
+        <v>0.003416152359688695</v>
       </c>
       <c r="AJ2">
-        <v>-0.02772561231685961</v>
+        <v>-0.04898645728103304</v>
       </c>
       <c r="AK2">
-        <v>-0.03977597829505539</v>
+        <v>-0.07562140871707078</v>
       </c>
       <c r="AL2">
-        <v>0.045</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AM2">
-        <v>0.045</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AN2">
-        <v>0.03875536480686696</v>
+        <v>0.01544728434504792</v>
       </c>
       <c r="AO2">
-        <v>491.1111111111111</v>
+        <v>720</v>
       </c>
       <c r="AP2">
-        <v>-0.4505150214592274</v>
+        <v>-0.3168210862619809</v>
       </c>
       <c r="AQ2">
-        <v>491.1111111111111</v>
+        <v>720</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.151</v>
+        <v>0.0496</v>
       </c>
       <c r="E3">
-        <v>-0.00471</v>
+        <v>0.181</v>
       </c>
       <c r="G3">
-        <v>0.05479930191972077</v>
+        <v>0.1344137273593899</v>
       </c>
       <c r="H3">
-        <v>0.05479930191972077</v>
+        <v>0.1344137273593899</v>
       </c>
       <c r="I3">
-        <v>0.07713787085514835</v>
+        <v>0.1944709246901812</v>
       </c>
       <c r="J3">
-        <v>0.06149324206915831</v>
+        <v>0.1558699120004216</v>
       </c>
       <c r="K3">
-        <v>36.5</v>
+        <v>63.2</v>
       </c>
       <c r="L3">
-        <v>0.1273996509598604</v>
+        <v>0.2008261836669845</v>
       </c>
       <c r="M3">
-        <v>17.4</v>
+        <v>55.2</v>
       </c>
       <c r="N3">
-        <v>0.04471858134155744</v>
+        <v>0.1299740993642571</v>
       </c>
       <c r="O3">
-        <v>0.4767123287671233</v>
+        <v>0.8734177215189873</v>
       </c>
       <c r="P3">
-        <v>17.4</v>
+        <v>55.2</v>
       </c>
       <c r="Q3">
-        <v>0.04471858134155744</v>
+        <v>0.1299740993642571</v>
       </c>
       <c r="R3">
-        <v>0.4767123287671233</v>
+        <v>0.8734177215189873</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>11.4</v>
+        <v>20.8</v>
       </c>
       <c r="V3">
-        <v>0.02929838087895142</v>
+        <v>0.04897574758653167</v>
       </c>
       <c r="W3">
-        <v>0.1303571428571429</v>
+        <v>0.2315018315018315</v>
       </c>
       <c r="X3">
-        <v>0.08774507814732951</v>
+        <v>0.0784179044057553</v>
       </c>
       <c r="Y3">
-        <v>0.04261206470981335</v>
+        <v>0.1530839270960762</v>
       </c>
       <c r="Z3">
-        <v>1.090514616321559</v>
+        <v>1.198843441789236</v>
       </c>
       <c r="AA3">
-        <v>0.06705927928141693</v>
+        <v>0.1868636217739708</v>
       </c>
       <c r="AB3">
-        <v>0.08767459892307401</v>
+        <v>0.07834271670054013</v>
       </c>
       <c r="AC3">
-        <v>-0.02061531964165708</v>
+        <v>0.1085209050734307</v>
       </c>
       <c r="AD3">
-        <v>0.903</v>
+        <v>0.967</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.903</v>
+        <v>0.967</v>
       </c>
       <c r="AG3">
-        <v>-10.497</v>
+        <v>-19.833</v>
       </c>
       <c r="AH3">
-        <v>0.002315366804870731</v>
+        <v>0.002271728839679844</v>
       </c>
       <c r="AI3">
-        <v>0.003280022375346437</v>
+        <v>0.003416152359688695</v>
       </c>
       <c r="AJ3">
-        <v>-0.02772561231685961</v>
+        <v>-0.04898645728103304</v>
       </c>
       <c r="AK3">
-        <v>-0.03977597829505539</v>
+        <v>-0.07562140871707078</v>
       </c>
       <c r="AL3">
-        <v>0.045</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AM3">
-        <v>0.045</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AN3">
-        <v>0.03875536480686696</v>
+        <v>0.01544728434504792</v>
       </c>
       <c r="AO3">
-        <v>491.1111111111111</v>
+        <v>720</v>
       </c>
       <c r="AP3">
-        <v>-0.4505150214592274</v>
+        <v>-0.3168210862619809</v>
       </c>
       <c r="AQ3">
-        <v>491.1111111111111</v>
+        <v>720</v>
       </c>
     </row>
   </sheetData>
